--- a/data/midjourney_korea_sref_codes.xlsx
+++ b/data/midjourney_korea_sref_codes.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sref_codes" sheetId="1" r:id="R6af890c34ccf4372"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출현_근거" sheetId="2" r:id="R72607d1964904e04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검수_제외" sheetId="3" r:id="Rd1a2ee0decbe406d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="4" r:id="Rff72aceaf7dd462c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sref_codes" sheetId="1" r:id="R6e1c9a33129046f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출현_근거" sheetId="2" r:id="R00b19f83ebb940c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검수_제외" sheetId="3" r:id="R5c5185d051454257"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="4" r:id="Rb6a73a32287b4d21"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -44,7 +44,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -81,59 +81,37 @@
         <x:fgColor rgb="FFD9EAD3"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAD3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="14">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="66">
+  <x:cellXfs count="73">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -252,6 +230,21 @@
     <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -4344,10 +4337,305 @@
         <x:v>251160</x:v>
       </x:c>
     </x:row>
+    <x:row r="780">
+      <x:c r="A780" s="12" t="str">
+        <x:v>3186922520</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="781">
+      <x:c r="A781" s="12" t="str">
+        <x:v>1938142599</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="782">
+      <x:c r="A782" s="12" t="str">
+        <x:v>3126422357</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="783">
+      <x:c r="A783" s="12" t="str">
+        <x:v>1636187491</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="784">
+      <x:c r="A784" s="12" t="str">
+        <x:v>2354286329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="785">
+      <x:c r="A785" s="12" t="str">
+        <x:v>4279378489</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="786">
+      <x:c r="A786" s="12" t="str">
+        <x:v>2082504830</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="787">
+      <x:c r="A787" s="12" t="str">
+        <x:v>2446808103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="788">
+      <x:c r="A788" s="12" t="str">
+        <x:v>2533808451</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="789">
+      <x:c r="A789" s="12" t="str">
+        <x:v>1407594300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="790">
+      <x:c r="A790" s="12" t="str">
+        <x:v>125392732</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="791">
+      <x:c r="A791" s="12" t="str">
+        <x:v>882099493</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="792">
+      <x:c r="A792" s="12" t="str">
+        <x:v>1786945130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="793">
+      <x:c r="A793" s="12" t="str">
+        <x:v>2979786966</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="794">
+      <x:c r="A794" s="12" t="str">
+        <x:v>4094740976</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="795">
+      <x:c r="A795" s="12" t="str">
+        <x:v>1254428622</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="796">
+      <x:c r="A796" s="12" t="str">
+        <x:v>2569822313</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="797">
+      <x:c r="A797" s="12" t="str">
+        <x:v>42780966</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="798">
+      <x:c r="A798" s="12" t="str">
+        <x:v>407314586</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="799">
+      <x:c r="A799" s="12" t="str">
+        <x:v>2636116336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="800">
+      <x:c r="A800" s="12" t="str">
+        <x:v>1243713023</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="801">
+      <x:c r="A801" s="12" t="str">
+        <x:v>4282282105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="802">
+      <x:c r="A802" s="12" t="str">
+        <x:v>1664242753</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="803">
+      <x:c r="A803" s="12" t="str">
+        <x:v>2031376966</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="804">
+      <x:c r="A804" s="12" t="str">
+        <x:v>3623850304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="805">
+      <x:c r="A805" s="12" t="str">
+        <x:v>3372067758</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="806">
+      <x:c r="A806" s="12" t="str">
+        <x:v>3169517328</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="807">
+      <x:c r="A807" s="12" t="str">
+        <x:v>3486953960</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="808">
+      <x:c r="A808" s="12" t="str">
+        <x:v>1620192228</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="809">
+      <x:c r="A809" s="12" t="str">
+        <x:v>2596889884</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="810">
+      <x:c r="A810" s="12" t="str">
+        <x:v>2187732243</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="811">
+      <x:c r="A811" s="12" t="str">
+        <x:v>2921367196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="812">
+      <x:c r="A812" s="12" t="str">
+        <x:v>3169921251</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="813">
+      <x:c r="A813" s="12" t="str">
+        <x:v>3962115437</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="814">
+      <x:c r="A814" s="12" t="str">
+        <x:v>984928173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="815">
+      <x:c r="A815" s="12" t="str">
+        <x:v>1025158517</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="816">
+      <x:c r="A816" s="12" t="str">
+        <x:v>7983081597</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="817">
+      <x:c r="A817" s="12" t="str">
+        <x:v>3959988404</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="818">
+      <x:c r="A818" s="12" t="str">
+        <x:v>838418117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="819">
+      <x:c r="A819" s="12" t="str">
+        <x:v>1982769432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="820">
+      <x:c r="A820" s="12" t="str">
+        <x:v>3326829432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="821">
+      <x:c r="A821" s="12" t="str">
+        <x:v>2588640818</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="822">
+      <x:c r="A822" s="12" t="str">
+        <x:v>1699009422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="823">
+      <x:c r="A823" s="12" t="str">
+        <x:v>1235558871</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="824">
+      <x:c r="A824" s="12" t="str">
+        <x:v>2189815634</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="825">
+      <x:c r="A825" s="12" t="str">
+        <x:v>28716490</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="826">
+      <x:c r="A826" s="12" t="str">
+        <x:v>3859943964</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="827">
+      <x:c r="A827" s="12" t="str">
+        <x:v>1797352086</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="828">
+      <x:c r="A828" s="12" t="str">
+        <x:v>2308724876</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="829">
+      <x:c r="A829" s="12" t="str">
+        <x:v>1168432014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="830">
+      <x:c r="A830" s="12" t="str">
+        <x:v>3694533790</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="831">
+      <x:c r="A831" s="12" t="str">
+        <x:v>3930069370</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="832">
+      <x:c r="A832" s="12" t="str">
+        <x:v>100535674</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="833">
+      <x:c r="A833" s="12" t="str">
+        <x:v>4145962190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="834">
+      <x:c r="A834" s="12" t="str">
+        <x:v>1104907777</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="835">
+      <x:c r="A835" s="12" t="str">
+        <x:v>4197443709</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="836">
+      <x:c r="A836" s="12" t="str">
+        <x:v>658450503</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="837">
+      <x:c r="A837" s="12" t="str">
+        <x:v>3181942011</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="838">
+      <x:c r="A838" s="12" t="str">
+        <x:v>4371870492</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1665299e5d794333"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6335dbcd4e7e4071"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4357,11 +4645,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="9" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="11" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="72" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="65" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -23544,10 +23832,1470 @@
         <x:v>--sref 286580 251160</x:v>
       </x:c>
     </x:row>
+    <x:row r="960">
+      <x:c r="A960" s="2" t="str">
+        <x:v>3186922520</x:v>
+      </x:c>
+      <x:c r="B960" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C960" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D960" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E960" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F960" s="18" t="str">
+        <x:v>--sref 3186922520</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="961">
+      <x:c r="A961" s="2" t="str">
+        <x:v>1938142599</x:v>
+      </x:c>
+      <x:c r="B961" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C961" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D961" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E961" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F961" s="18" t="str">
+        <x:v>--sref 1938142599</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="962">
+      <x:c r="A962" s="2" t="str">
+        <x:v>3126422357</x:v>
+      </x:c>
+      <x:c r="B962" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C962" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D962" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E962" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F962" s="18" t="str">
+        <x:v>--sref 3126422357</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="963">
+      <x:c r="A963" s="2" t="str">
+        <x:v>1636187491</x:v>
+      </x:c>
+      <x:c r="B963" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C963" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D963" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E963" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F963" s="18" t="str">
+        <x:v>--sref 1636187491 2354286329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="964">
+      <x:c r="A964" s="2" t="str">
+        <x:v>2354286329</x:v>
+      </x:c>
+      <x:c r="B964" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C964" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D964" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E964" s="16" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F964" s="18" t="str">
+        <x:v>--sref 1636187491 2354286329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="965">
+      <x:c r="A965" s="2" t="str">
+        <x:v>4279378489</x:v>
+      </x:c>
+      <x:c r="B965" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C965" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D965" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E965" s="16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F965" s="18" t="str">
+        <x:v>--sref 4279378489</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="966">
+      <x:c r="A966" s="2" t="str">
+        <x:v>2082504830</x:v>
+      </x:c>
+      <x:c r="B966" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C966" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D966" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E966" s="16" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F966" s="18" t="str">
+        <x:v>--sref 2082504830</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="967">
+      <x:c r="A967" s="2" t="str">
+        <x:v>2446808103</x:v>
+      </x:c>
+      <x:c r="B967" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C967" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D967" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E967" s="16" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F967" s="18" t="str">
+        <x:v>--sref 2446808103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="968">
+      <x:c r="A968" s="2" t="str">
+        <x:v>2533808451</x:v>
+      </x:c>
+      <x:c r="B968" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C968" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D968" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E968" s="16" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F968" s="18" t="str">
+        <x:v>--sref 2533808451</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="969">
+      <x:c r="A969" s="2" t="str">
+        <x:v>2533808451</x:v>
+      </x:c>
+      <x:c r="B969" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C969" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D969" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E969" s="16" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F969" s="18" t="str">
+        <x:v>--sref 2533808451 --niji 7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="970">
+      <x:c r="A970" s="2" t="str">
+        <x:v>1407594300</x:v>
+      </x:c>
+      <x:c r="B970" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C970" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D970" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E970" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F970" s="18" t="str">
+        <x:v>--sref 1407594300 125392732</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="971">
+      <x:c r="A971" s="2" t="str">
+        <x:v>125392732</x:v>
+      </x:c>
+      <x:c r="B971" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C971" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D971" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E971" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F971" s="18" t="str">
+        <x:v>--sref 1407594300 125392732</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="972">
+      <x:c r="A972" s="2" t="str">
+        <x:v>882099493</x:v>
+      </x:c>
+      <x:c r="B972" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C972" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D972" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E972" s="16" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F972" s="18" t="str">
+        <x:v>--sref 882099493</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="973">
+      <x:c r="A973" s="2" t="str">
+        <x:v>1938142599</x:v>
+      </x:c>
+      <x:c r="B973" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C973" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D973" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E973" s="16" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F973" s="18" t="str">
+        <x:v>--sref 1938142599 2354286329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="974">
+      <x:c r="A974" s="2" t="str">
+        <x:v>2354286329</x:v>
+      </x:c>
+      <x:c r="B974" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C974" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D974" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E974" s="16" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F974" s="18" t="str">
+        <x:v>--sref 1938142599 2354286329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="975">
+      <x:c r="A975" s="2" t="str">
+        <x:v>1786945130</x:v>
+      </x:c>
+      <x:c r="B975" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C975" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D975" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E975" s="16" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F975" s="18" t="str">
+        <x:v>--sref 1786945130 2979786966 4094740976 1254428622 2569822313</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="976">
+      <x:c r="A976" s="2" t="str">
+        <x:v>2979786966</x:v>
+      </x:c>
+      <x:c r="B976" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C976" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D976" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E976" s="16" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F976" s="18" t="str">
+        <x:v>--sref 1786945130 2979786966 4094740976 1254428622 2569822313</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="977">
+      <x:c r="A977" s="2" t="str">
+        <x:v>4094740976</x:v>
+      </x:c>
+      <x:c r="B977" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C977" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D977" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E977" s="16" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F977" s="18" t="str">
+        <x:v>--sref 1786945130 2979786966 4094740976 1254428622 2569822313</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="978">
+      <x:c r="A978" s="2" t="str">
+        <x:v>1254428622</x:v>
+      </x:c>
+      <x:c r="B978" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C978" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D978" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E978" s="16" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F978" s="18" t="str">
+        <x:v>--sref 1786945130 2979786966 4094740976 1254428622 2569822313</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="979">
+      <x:c r="A979" s="2" t="str">
+        <x:v>2569822313</x:v>
+      </x:c>
+      <x:c r="B979" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C979" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D979" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E979" s="16" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F979" s="18" t="str">
+        <x:v>--sref 1786945130 2979786966 4094740976 1254428622 2569822313</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="980">
+      <x:c r="A980" s="2" t="str">
+        <x:v>42780966</x:v>
+      </x:c>
+      <x:c r="B980" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C980" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D980" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E980" s="16" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F980" s="18" t="str">
+        <x:v>--sref 42780966</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="981">
+      <x:c r="A981" s="2" t="str">
+        <x:v>407314586</x:v>
+      </x:c>
+      <x:c r="B981" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C981" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D981" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E981" s="16" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F981" s="18" t="str">
+        <x:v>--sref 407314586</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="982">
+      <x:c r="A982" s="2" t="str">
+        <x:v>2636116336</x:v>
+      </x:c>
+      <x:c r="B982" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C982" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D982" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E982" s="16" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F982" s="18" t="str">
+        <x:v>--sref 2636116336 1243713023 407314586</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="983">
+      <x:c r="A983" s="2" t="str">
+        <x:v>1243713023</x:v>
+      </x:c>
+      <x:c r="B983" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C983" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D983" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E983" s="16" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F983" s="18" t="str">
+        <x:v>--sref 2636116336 1243713023 407314586</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="984">
+      <x:c r="A984" s="2" t="str">
+        <x:v>407314586</x:v>
+      </x:c>
+      <x:c r="B984" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C984" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D984" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E984" s="16" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F984" s="18" t="str">
+        <x:v>--sref 2636116336 1243713023 407314586</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="985">
+      <x:c r="A985" s="2" t="str">
+        <x:v>42780966</x:v>
+      </x:c>
+      <x:c r="B985" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C985" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D985" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E985" s="16" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F985" s="18" t="str">
+        <x:v>--sref 42780966 4282282105 1664242753</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="986">
+      <x:c r="A986" s="2" t="str">
+        <x:v>4282282105</x:v>
+      </x:c>
+      <x:c r="B986" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C986" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D986" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E986" s="16" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F986" s="18" t="str">
+        <x:v>--sref 42780966 4282282105 1664242753</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="987">
+      <x:c r="A987" s="2" t="str">
+        <x:v>1664242753</x:v>
+      </x:c>
+      <x:c r="B987" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C987" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D987" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E987" s="16" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F987" s="18" t="str">
+        <x:v>--sref 42780966 4282282105 1664242753</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="988">
+      <x:c r="A988" s="2" t="str">
+        <x:v>2031376966</x:v>
+      </x:c>
+      <x:c r="B988" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C988" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D988" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E988" s="16" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F988" s="18" t="str">
+        <x:v>--sref 2031376966</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="989">
+      <x:c r="A989" s="2" t="str">
+        <x:v>3623850304</x:v>
+      </x:c>
+      <x:c r="B989" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C989" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D989" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E989" s="16" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F989" s="18" t="str">
+        <x:v>--sref 3623850304 --v 8.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="990">
+      <x:c r="A990" s="2" t="str">
+        <x:v>3372067758</x:v>
+      </x:c>
+      <x:c r="B990" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C990" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D990" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E990" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F990" s="18" t="str">
+        <x:v>--sref 3372067758 3169517328 3486953960</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="991">
+      <x:c r="A991" s="2" t="str">
+        <x:v>3169517328</x:v>
+      </x:c>
+      <x:c r="B991" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C991" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D991" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E991" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F991" s="18" t="str">
+        <x:v>--sref 3372067758 3169517328 3486953960</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="992">
+      <x:c r="A992" s="2" t="str">
+        <x:v>3486953960</x:v>
+      </x:c>
+      <x:c r="B992" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C992" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D992" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E992" s="16" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F992" s="18" t="str">
+        <x:v>--sref 3372067758 3169517328 3486953960</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="993">
+      <x:c r="A993" s="2" t="str">
+        <x:v>1620192228</x:v>
+      </x:c>
+      <x:c r="B993" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C993" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D993" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E993" s="16" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F993" s="18" t="str">
+        <x:v>--sref 1620192228</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="994">
+      <x:c r="A994" s="2" t="str">
+        <x:v>3169517328</x:v>
+      </x:c>
+      <x:c r="B994" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C994" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D994" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E994" s="16" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F994" s="18" t="str">
+        <x:v>--sref 3169517328</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="995">
+      <x:c r="A995" s="2" t="str">
+        <x:v>2596889884</x:v>
+      </x:c>
+      <x:c r="B995" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C995" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D995" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E995" s="16" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F995" s="18" t="str">
+        <x:v>--sref 2596889884</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="996">
+      <x:c r="A996" s="2" t="str">
+        <x:v>2187732243</x:v>
+      </x:c>
+      <x:c r="B996" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C996" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D996" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E996" s="16" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F996" s="18" t="str">
+        <x:v>--sref 2187732243</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="997">
+      <x:c r="A997" s="2" t="str">
+        <x:v>2921367196</x:v>
+      </x:c>
+      <x:c r="B997" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C997" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D997" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E997" s="16" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F997" s="18" t="str">
+        <x:v>--sref 2921367196 --niji 7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="998">
+      <x:c r="A998" s="2" t="str">
+        <x:v>2921367196</x:v>
+      </x:c>
+      <x:c r="B998" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C998" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D998" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E998" s="16" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F998" s="18" t="str">
+        <x:v>--sref 2921367196 917326586 --niji 7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="999">
+      <x:c r="A999" s="2" t="str">
+        <x:v>917326586</x:v>
+      </x:c>
+      <x:c r="B999" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C999" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D999" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E999" s="16" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F999" s="18" t="str">
+        <x:v>--sref 2921367196 917326586 --niji 7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1000">
+      <x:c r="A1000" s="2" t="str">
+        <x:v>3169921251</x:v>
+      </x:c>
+      <x:c r="B1000" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1000" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1000" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1000" s="16" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F1000" s="18" t="str">
+        <x:v>--sref 3169921251</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1001">
+      <x:c r="A1001" s="2" t="str">
+        <x:v>3962115437</x:v>
+      </x:c>
+      <x:c r="B1001" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1001" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1001" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1001" s="16" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F1001" s="18" t="str">
+        <x:v>--sref 3962115437 984928173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1002">
+      <x:c r="A1002" s="2" t="str">
+        <x:v>984928173</x:v>
+      </x:c>
+      <x:c r="B1002" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1002" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1002" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1002" s="16" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F1002" s="18" t="str">
+        <x:v>--sref 3962115437 984928173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1003">
+      <x:c r="A1003" s="2" t="str">
+        <x:v>3962115437</x:v>
+      </x:c>
+      <x:c r="B1003" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1003" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1003" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1003" s="16" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F1003" s="18" t="str">
+        <x:v>--sref 3962115437 1025158517</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1004">
+      <x:c r="A1004" s="2" t="str">
+        <x:v>1025158517</x:v>
+      </x:c>
+      <x:c r="B1004" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1004" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1004" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1004" s="16" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F1004" s="18" t="str">
+        <x:v>--sref 3962115437 1025158517</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1005">
+      <x:c r="A1005" s="2" t="str">
+        <x:v>984928173</x:v>
+      </x:c>
+      <x:c r="B1005" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1005" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1005" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1005" s="16" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F1005" s="18" t="str">
+        <x:v>--sref 984928173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1006">
+      <x:c r="A1006" s="2" t="str">
+        <x:v>7983081597</x:v>
+      </x:c>
+      <x:c r="B1006" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1006" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1006" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1006" s="16" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F1006" s="18" t="str">
+        <x:v>--sref 7983081597</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1007">
+      <x:c r="A1007" s="2" t="str">
+        <x:v>3959988404</x:v>
+      </x:c>
+      <x:c r="B1007" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1007" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1007" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1007" s="16" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F1007" s="18" t="str">
+        <x:v>--sref 3959988404</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1008">
+      <x:c r="A1008" s="2" t="str">
+        <x:v>838418117</x:v>
+      </x:c>
+      <x:c r="B1008" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1008" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1008" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1008" s="16" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F1008" s="18" t="str">
+        <x:v>--sref 838418117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1009">
+      <x:c r="A1009" s="2" t="str">
+        <x:v>1982769432</x:v>
+      </x:c>
+      <x:c r="B1009" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1009" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1009" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1009" s="16" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F1009" s="18" t="str">
+        <x:v>--sref 1982769432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1010">
+      <x:c r="A1010" s="2" t="str">
+        <x:v>3326829432</x:v>
+      </x:c>
+      <x:c r="B1010" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1010" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1010" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1010" s="16" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F1010" s="18" t="str">
+        <x:v>--sref 3326829432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1011">
+      <x:c r="A1011" s="2" t="str">
+        <x:v>2588640818</x:v>
+      </x:c>
+      <x:c r="B1011" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1011" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1011" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1011" s="16" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1011" s="18" t="str">
+        <x:v>--sref 2588640818 1699009422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1012">
+      <x:c r="A1012" s="2" t="str">
+        <x:v>1699009422</x:v>
+      </x:c>
+      <x:c r="B1012" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1012" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1012" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1012" s="16" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1012" s="18" t="str">
+        <x:v>--sref 2588640818 1699009422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1013">
+      <x:c r="A1013" s="2" t="str">
+        <x:v>1235558871</x:v>
+      </x:c>
+      <x:c r="B1013" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1013" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1013" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1013" s="16" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F1013" s="18" t="str">
+        <x:v>--sref 1235558871::1 --niji 7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1014">
+      <x:c r="A1014" s="2" t="str">
+        <x:v>2189815634</x:v>
+      </x:c>
+      <x:c r="B1014" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1014" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1014" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1014" s="16" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F1014" s="18" t="str">
+        <x:v>--sref 2189815634</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1015">
+      <x:c r="A1015" s="2" t="str">
+        <x:v>28716490</x:v>
+      </x:c>
+      <x:c r="B1015" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1015" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1015" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1015" s="16" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F1015" s="18" t="str">
+        <x:v>--sref 28716490</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1016">
+      <x:c r="A1016" s="2" t="str">
+        <x:v>3859943964</x:v>
+      </x:c>
+      <x:c r="B1016" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1016" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1016" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1016" s="16" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F1016" s="18" t="str">
+        <x:v>--sref 3859943964 838418117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1017">
+      <x:c r="A1017" s="2" t="str">
+        <x:v>838418117</x:v>
+      </x:c>
+      <x:c r="B1017" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1017" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1017" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1017" s="16" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F1017" s="18" t="str">
+        <x:v>--sref 3859943964 838418117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1018">
+      <x:c r="A1018" s="2" t="str">
+        <x:v>1797352086</x:v>
+      </x:c>
+      <x:c r="B1018" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1018" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1018" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1018" s="16" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F1018" s="18" t="str">
+        <x:v>--sref 1797352086 2308724876</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1019">
+      <x:c r="A1019" s="2" t="str">
+        <x:v>2308724876</x:v>
+      </x:c>
+      <x:c r="B1019" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1019" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1019" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1019" s="16" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F1019" s="18" t="str">
+        <x:v>--sref 1797352086 2308724876</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1020">
+      <x:c r="A1020" s="2" t="str">
+        <x:v>1797352086</x:v>
+      </x:c>
+      <x:c r="B1020" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1020" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1020" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1020" s="16" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F1020" s="18" t="str">
+        <x:v>--sref 1797352086 2308724876 1168432014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1021">
+      <x:c r="A1021" s="2" t="str">
+        <x:v>2308724876</x:v>
+      </x:c>
+      <x:c r="B1021" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1021" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1021" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1021" s="16" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F1021" s="18" t="str">
+        <x:v>--sref 1797352086 2308724876 1168432014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1022">
+      <x:c r="A1022" s="2" t="str">
+        <x:v>1168432014</x:v>
+      </x:c>
+      <x:c r="B1022" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1022" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1022" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1022" s="16" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F1022" s="18" t="str">
+        <x:v>--sref 1797352086 2308724876 1168432014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1023">
+      <x:c r="A1023" s="2" t="str">
+        <x:v>3694533790</x:v>
+      </x:c>
+      <x:c r="B1023" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1023" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1023" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1023" s="16" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F1023" s="18" t="str">
+        <x:v>--sref 3694533790</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1024">
+      <x:c r="A1024" s="2" t="str">
+        <x:v>3930069370</x:v>
+      </x:c>
+      <x:c r="B1024" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1024" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1024" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1024" s="16" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F1024" s="18" t="str">
+        <x:v>--sref 3930069370</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1025">
+      <x:c r="A1025" s="2" t="str">
+        <x:v>100535674</x:v>
+      </x:c>
+      <x:c r="B1025" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1025" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1025" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1025" s="16" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F1025" s="18" t="str">
+        <x:v>--sref 100535674</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1026">
+      <x:c r="A1026" s="2" t="str">
+        <x:v>4145962190</x:v>
+      </x:c>
+      <x:c r="B1026" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1026" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1026" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1026" s="16" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F1026" s="18" t="str">
+        <x:v>--sref 4145962190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1027">
+      <x:c r="A1027" s="2" t="str">
+        <x:v>1104907777</x:v>
+      </x:c>
+      <x:c r="B1027" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1027" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1027" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1027" s="16" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F1027" s="18" t="str">
+        <x:v>--sref 1104907777</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1028">
+      <x:c r="A1028" s="2" t="str">
+        <x:v>4197443709</x:v>
+      </x:c>
+      <x:c r="B1028" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1028" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1028" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1028" s="16" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F1028" s="18" t="str">
+        <x:v>--sref 4197443709::1 --niji 7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1029">
+      <x:c r="A1029" s="2" t="str">
+        <x:v>658450503</x:v>
+      </x:c>
+      <x:c r="B1029" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1029" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1029" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1029" s="16" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F1029" s="18" t="str">
+        <x:v>--sref 658450503</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1030">
+      <x:c r="A1030" s="2" t="str">
+        <x:v>3181942011</x:v>
+      </x:c>
+      <x:c r="B1030" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1030" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1030" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1030" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F1030" s="18" t="str">
+        <x:v>--sref 3181942011</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1031">
+      <x:c r="A1031" s="2" t="str">
+        <x:v>4371870492</x:v>
+      </x:c>
+      <x:c r="B1031" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1031" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1031" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1031" s="16" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F1031" s="18" t="str">
+        <x:v>--sref 4371870492</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1032">
+      <x:c r="A1032" s="2" t="str">
+        <x:v>4371870492</x:v>
+      </x:c>
+      <x:c r="B1032" s="14" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1032" t="str">
+        <x:v>01:24</x:v>
+      </x:c>
+      <x:c r="D1032" t="str">
+        <x:v>사용자 직접 제공</x:v>
+      </x:c>
+      <x:c r="E1032" s="16" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F1032" s="18" t="str">
+        <x:v>--sref 4371870492 (--profile op2hwq1과 함께)</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba786dc923444fc4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R451bab2b1c2d4774"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23622,13 +25370,13 @@
         <x:v>reboot</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>명확한 제외</x:v>
+        <x:v>원본 자료 제외 · 사용자 직접 재등록</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
-        <x:v>SREF 코드와 동일 메시지에 '언제나 그랬듯이 이방에서만'이라고 명시</x:v>
+        <x:v>원본 메시지의 방 한정 문구로 최초 검수에서는 제외했으나, 2026-08-03 사용자가 직접 DB 추가를 요청하여 최종 DB에는 포함</x:v>
       </x:c>
       <x:c r="F3" s="18" t="str">
-        <x:v>차분한 쿨톤과 심도를 조정하여 만든 실사 sref코드 … --sref 4371870492 … 언제나 그랬듯이 이방에서만 ^^</x:v>
+        <x:v>원본: 차분한 쿨톤과 심도를 조정하여 만든 실사 sref코드 … --sref 4371870492 … 언제나 그랬듯이 이방에서만 ^^ | 재등록: 사용자 직접 제공 --sref 4371870492</x:v>
       </x:c>
       <x:c r="G3" t="n">
         <x:v>19149</x:v>
@@ -23637,7 +25385,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d030adeee2d478c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf75f18ce6b9746fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23646,17 +25394,17 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="64" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="39" t="str">
-        <x:v>Midjourney Korea SREF 추출 결과</x:v>
-      </x:c>
-      <x:c r="B1" s="39"/>
+      <x:c r="A1" s="70" t="str">
+        <x:v>Midjourney Korea SREF 통합 결과</x:v>
+      </x:c>
+      <x:c r="B1" s="70"/>
       <x:c r="C1" s="39"/>
       <x:c r="D1" s="39"/>
     </x:row>
@@ -23673,7 +25421,7 @@
         <x:v>전체 SREF 출현 수</x:v>
       </x:c>
       <x:c r="B4" s="53" t="n">
-        <x:v>967</x:v>
+        <x:v>1040</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -23681,15 +25429,15 @@
         <x:v>전체 고유 SREF 수</x:v>
       </x:c>
       <x:c r="B5" s="53" t="n">
-        <x:v>780</x:v>
+        <x:v>838</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="52" t="str">
-        <x:v>제외 고유 코드 수</x:v>
+        <x:v>현재 제외 고유 코드 수</x:v>
       </x:c>
       <x:c r="B6" s="53" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -23697,7 +25445,7 @@
         <x:v>최종 수집 고유 코드 수</x:v>
       </x:c>
       <x:c r="B7" s="53" t="n">
-        <x:v>778</x:v>
+        <x:v>837</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -23705,14 +25453,14 @@
         <x:v>최종 수집 출현 수</x:v>
       </x:c>
       <x:c r="B8" s="55" t="n">
-        <x:v>958</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="63" t="str">
+        <x:v>1031</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="22" customHeight="1">
+      <x:c r="A10" s="71" t="str">
         <x:v>추출·검수 기준</x:v>
       </x:c>
-      <x:c r="B10" s="63"/>
+      <x:c r="B10" s="71"/>
       <x:c r="C10" s="63"/>
       <x:c r="D10" s="63"/>
     </x:row>
@@ -23766,10 +25514,65 @@
       <x:c r="C15" s="18" t="str"/>
       <x:c r="D15" s="18" t="str"/>
     </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17" s="71" t="str">
+        <x:v>2026-08-03 DB·엑셀 동기화</x:v>
+      </x:c>
+      <x:c r="B17" s="71"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="66" t="str">
+        <x:v>사용자 입력 SREF 출현 수</x:v>
+      </x:c>
+      <x:c r="B18" s="66" t="n">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="66" t="str">
+        <x:v>사용자 입력 고유 코드 수</x:v>
+      </x:c>
+      <x:c r="B19" s="66" t="n">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="66" t="str">
+        <x:v>기존 DB 중복 코드 수</x:v>
+      </x:c>
+      <x:c r="B20" s="66" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="66" t="str">
+        <x:v>실제 신규 추가 코드 수</x:v>
+      </x:c>
+      <x:c r="B21" s="66" t="n">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="66" t="str">
+        <x:v>최종 프로그램 DB 코드 수</x:v>
+      </x:c>
+      <x:c r="B22" s="66" t="n">
+        <x:v>837</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="38" customHeight="1">
+      <x:c r="A23" s="72" t="str">
+        <x:v>재등록 처리</x:v>
+      </x:c>
+      <x:c r="B23" s="72" t="str">
+        <x:v>4371870492는 원본 자료에서는 제외됐으나 사용자의 직접 추가 요청으로 최종 DB와 엑셀에 포함</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A10:D10"/>
+    <x:mergeCell ref="A1:B1"/>
+    <x:mergeCell ref="A10:B10"/>
+    <x:mergeCell ref="A17:B17"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
